--- a/management_forms/001_a3_problem_solving_report--management_forms.xlsx
+++ b/management_forms/001_a3_problem_solving_report--management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -989,8 +989,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'manpower',_'value':_'manpower'}</t>
+          <t>manpower</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Manpower', 'value': 'manpower'}</t>
+          <t>Manpower</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'method',_'value':_'method'}</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Method', 'value': 'method'}</t>
+          <t>Method</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'material',_'value':_'material'}</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Material', 'value': 'material'}</t>
+          <t>Material</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'machine',_'value':_'machine'}</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Machine', 'value': 'machine'}</t>
+          <t>Machine</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'measurement',_'value':_'measurement'}</t>
+          <t>measurement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Measurement', 'value': 'measurement'}</t>
+          <t>Measurement</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'environment',_'value':_'environment'}</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Environment', 'value': 'environment'}</t>
+          <t>Environment</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'draft',_'value':_'draft'}</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Draft', 'value': 'draft'}</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'under_review',_'value':_'under_review'}</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Under Review', 'value': 'under_review'}</t>
+          <t>Under Review</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Approved', 'value': 'approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
